--- a/251202_pairwise_distances.xlsx
+++ b/251202_pairwise_distances.xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vtioffice365-my.sharepoint.com/personal/elric_milet-vti-se/Documents/Thesis/TerminalCongestionViewer/TerminalCongestionViewer/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_FF001D98C1E6F80578F00C481ABB1A916BCFDAA0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8917915-92C9-43B1-BA90-8A5319CF3987}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="28680" yWindow="-3795" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="251202_pairwise_distances" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="251202_pairwise_distances" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -20,98 +36,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="21">
   <si>
-    <t xml:space="preserve">traj1</t>
+    <t>traj1</t>
   </si>
   <si>
-    <t xml:space="preserve">traj2</t>
+    <t>traj2</t>
   </si>
   <si>
-    <t xml:space="preserve">sspd</t>
+    <t>sspd</t>
   </si>
   <si>
-    <t xml:space="preserve">dfd</t>
+    <t>dfd</t>
   </si>
   <si>
-    <t xml:space="preserve">edr</t>
+    <t>edr</t>
   </si>
   <si>
-    <t xml:space="preserve">1-sspd*10000</t>
+    <t>1-sspd*10000</t>
   </si>
   <si>
-    <t xml:space="preserve">1-dfd*10000</t>
+    <t>1-dfd*10000</t>
   </si>
   <si>
-    <t xml:space="preserve">subj. local</t>
+    <t>subj. local</t>
   </si>
   <si>
-    <t xml:space="preserve">subj. global</t>
+    <t>subj. global</t>
   </si>
   <si>
-    <t xml:space="preserve">norm. edr</t>
+    <t>norm. edr</t>
   </si>
   <si>
-    <t xml:space="preserve">norm. 1-sspd</t>
+    <t>norm. 1-sspd</t>
   </si>
   <si>
-    <t xml:space="preserve">norm. 1-dfd</t>
+    <t>norm. 1-dfd</t>
   </si>
   <si>
-    <t xml:space="preserve">norm. subj. loc.</t>
+    <t>norm. subj. loc.</t>
   </si>
   <si>
-    <t xml:space="preserve">norm. subj. glob.</t>
+    <t>norm. subj. glob.</t>
   </si>
   <si>
-    <t xml:space="preserve">55700000076548472</t>
+    <t>55700000076548472</t>
   </si>
   <si>
-    <t xml:space="preserve">55700000076547896</t>
+    <t>55700000076547896</t>
   </si>
   <si>
-    <t xml:space="preserve">55700000076547865</t>
+    <t>55700000076547865</t>
   </si>
   <si>
-    <t xml:space="preserve">55700000076547834</t>
+    <t>55700000076547834</t>
   </si>
   <si>
-    <t xml:space="preserve">55700000076546593</t>
+    <t>55700000076546593</t>
   </si>
   <si>
-    <t xml:space="preserve">55700000076546624</t>
+    <t>55700000076546624</t>
+  </si>
+  <si>
+    <t>7 13 14</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000000000000000000"/>
-    <numFmt numFmtId="167" formatCode="#,##0.000000000000000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.00000000000000000000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000000000000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -123,7 +125,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -131,61 +133,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -244,18 +208,37 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -265,7 +248,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>251202_pairwise_distances!$K$1</c:f>
+              <c:f>'251202_pairwise_distances'!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -284,16 +267,24 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="sv-SE"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -301,26 +292,27 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="0">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>251202_pairwise_distances!$K$2:$K$16</c:f>
+              <c:f>'251202_pairwise_distances'!$K$2:$K$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -328,57 +320,62 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.705421070576202</c:v>
+                  <c:v>0.70542107057620262</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.907944084555063</c:v>
+                  <c:v>0.90794408455506359</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.631776338220252</c:v>
+                  <c:v>0.6317763382202517</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.392831201174047</c:v>
+                  <c:v>0.39283120117404752</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.424650528469144</c:v>
+                  <c:v>0.4246505284691442</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.498895625491039</c:v>
+                  <c:v>0.49889562549103966</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.817088898442017</c:v>
+                  <c:v>0.81708889844201671</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.252983293556086</c:v>
+                  <c:v>0.25298329355608618</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.136348138734774</c:v>
+                  <c:v>0.13634813873477553</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.267338153337306</c:v>
+                  <c:v>0.26733815333730709</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.280088646437095</c:v>
+                  <c:v>0.28008864643709463</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.153596999659052</c:v>
+                  <c:v>0.15359699965905149</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.267338153337306</c:v>
+                  <c:v>0.26733815333730709</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D758-4A99-9A1B-E47195F96422}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>251202_pairwise_distances!$L$1</c:f>
+              <c:f>'251202_pairwise_distances'!$L$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -389,7 +386,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ff420e"/>
+              <a:srgbClr val="FF420E"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -397,16 +394,24 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="sv-SE"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -414,84 +419,90 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="0">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>251202_pairwise_distances!$L$2:$L$16</c:f>
+              <c:f>'251202_pairwise_distances'!$L$2:$L$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.924367744880404</c:v>
+                  <c:v>0.92436774488040274</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.207655027063344</c:v>
+                  <c:v>0.20765502706334077</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.678075774450885</c:v>
+                  <c:v>0.67807577445088396</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.782356820482973</c:v>
+                  <c:v>0.7823568204829715</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.747076659214157</c:v>
+                  <c:v>0.74707665921415489</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.49735927965392</c:v>
+                  <c:v>0.49735927965391669</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.881876896150718</c:v>
+                  <c:v>0.88187689615071829</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.927681701558628</c:v>
+                  <c:v>0.92768170155862573</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.638310943074958</c:v>
+                  <c:v>0.63831094307495673</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.350593297829709</c:v>
+                  <c:v>0.35059329782970872</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.838584978682301</c:v>
+                  <c:v>0.8385849786823002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.831397228300744</c:v>
+                  <c:v>0.83139722830074225</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.99301676060078</c:v>
+                  <c:v>0.99301676060078015</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D758-4A99-9A1B-E47195F96422}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>251202_pairwise_distances!$M$1</c:f>
+              <c:f>'251202_pairwise_distances'!$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -502,7 +513,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ffd320"/>
+              <a:srgbClr val="FFD320"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -510,16 +521,24 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="sv-SE"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -527,40 +546,41 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="0">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>251202_pairwise_distances!$M$2:$M$16</c:f>
+              <c:f>'251202_pairwise_distances'!$M$2:$M$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.981924262846429</c:v>
+                  <c:v>0.98192426284642886</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0752150642869971</c:v>
+                  <c:v>7.5215064286997479E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0513282970862132</c:v>
+                  <c:v>5.1328297086212879E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.459016092969441</c:v>
+                  <c:v>0.45901609296944051</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1</c:v>
@@ -569,42 +589,47 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.297739497343149</c:v>
+                  <c:v>0.29773949734314903</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.864579228673523</c:v>
+                  <c:v>0.86457922867352255</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.850011389018827</c:v>
+                  <c:v>0.85001138901882678</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.634895451397799</c:v>
+                  <c:v>0.63489545139779835</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.0889461763362</c:v>
+                  <c:v>8.8946176336199556E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.0654438704879399</c:v>
+                  <c:v>6.5443870487939121E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.436317820001977</c:v>
+                  <c:v>0.43631782000197633</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.366997957526424</c:v>
+                  <c:v>0.36699795752642367</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.80878726192359</c:v>
+                  <c:v>0.80878726192359129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D758-4A99-9A1B-E47195F96422}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>251202_pairwise_distances!$N$1</c:f>
+              <c:f>'251202_pairwise_distances'!$N$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -615,7 +640,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="579d1c"/>
+              <a:srgbClr val="579D1C"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -623,16 +648,24 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="sv-SE"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -640,70 +673,71 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="0">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>251202_pairwise_distances!$N$2:$N$16</c:f>
+              <c:f>'251202_pairwise_distances'!$N$2:$N$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.5</c:v>
+                  <c:v>0.49999999999999989</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>0.49999999999999989</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.75</c:v>
+                  <c:v>0.75000000000000011</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5</c:v>
+                  <c:v>0.49999999999999989</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.75</c:v>
+                  <c:v>0.75000000000000011</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.25</c:v>
+                  <c:v>0.24999999999999994</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.75</c:v>
+                  <c:v>0.75000000000000011</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.5</c:v>
+                  <c:v>0.49999999999999989</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5</c:v>
+                  <c:v>0.49999999999999989</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.25</c:v>
+                  <c:v>0.24999999999999994</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.25</c:v>
+                  <c:v>0.24999999999999994</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.5</c:v>
+                  <c:v>0.49999999999999989</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>1</c:v>
@@ -711,9 +745,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-D758-4A99-9A1B-E47195F96422}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="100"/>
-        <c:overlap val="0"/>
         <c:axId val="90082218"/>
         <c:axId val="23213005"/>
       </c:barChart>
@@ -731,7 +777,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -740,11 +786,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="sv-SE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="23213005"/>
@@ -765,7 +812,7 @@
           <c:spPr>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
+                <a:srgbClr val="B3B3B3"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -777,7 +824,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -786,11 +833,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="sv-SE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="90082218"/>
@@ -801,7 +849,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="b3b3b3"/>
+            <a:srgbClr val="B3B3B3"/>
           </a:solidFill>
         </a:ln>
       </c:spPr>
@@ -820,35 +868,45 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
               <a:uFillTx/>
               <a:latin typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="sv-SE"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -858,7 +916,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>251202_pairwise_distances!$K$1</c:f>
+              <c:f>'251202_pairwise_distances'!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -877,16 +935,24 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="sv-SE"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -894,26 +960,27 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="0">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>251202_pairwise_distances!$K$2:$K$16</c:f>
+              <c:f>'251202_pairwise_distances'!$K$2:$K$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -921,57 +988,62 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.705421070576202</c:v>
+                  <c:v>0.70542107057620262</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.907944084555063</c:v>
+                  <c:v>0.90794408455506359</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.631776338220252</c:v>
+                  <c:v>0.6317763382202517</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.392831201174047</c:v>
+                  <c:v>0.39283120117404752</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.424650528469144</c:v>
+                  <c:v>0.4246505284691442</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.498895625491039</c:v>
+                  <c:v>0.49889562549103966</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.817088898442017</c:v>
+                  <c:v>0.81708889844201671</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.252983293556086</c:v>
+                  <c:v>0.25298329355608618</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.136348138734774</c:v>
+                  <c:v>0.13634813873477553</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.267338153337306</c:v>
+                  <c:v>0.26733815333730709</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.280088646437095</c:v>
+                  <c:v>0.28008864643709463</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.153596999659052</c:v>
+                  <c:v>0.15359699965905149</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.267338153337306</c:v>
+                  <c:v>0.26733815333730709</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9983-4F0F-80F4-002E112B287C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>251202_pairwise_distances!$L$1</c:f>
+              <c:f>'251202_pairwise_distances'!$L$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -982,7 +1054,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ff420e"/>
+              <a:srgbClr val="FF420E"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -990,16 +1062,24 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="sv-SE"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1007,84 +1087,90 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="0">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>251202_pairwise_distances!$L$2:$L$16</c:f>
+              <c:f>'251202_pairwise_distances'!$L$2:$L$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.924367744880404</c:v>
+                  <c:v>0.92436774488040274</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.207655027063344</c:v>
+                  <c:v>0.20765502706334077</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.678075774450885</c:v>
+                  <c:v>0.67807577445088396</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.782356820482973</c:v>
+                  <c:v>0.7823568204829715</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.747076659214157</c:v>
+                  <c:v>0.74707665921415489</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.49735927965392</c:v>
+                  <c:v>0.49735927965391669</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.881876896150718</c:v>
+                  <c:v>0.88187689615071829</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.927681701558628</c:v>
+                  <c:v>0.92768170155862573</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.638310943074958</c:v>
+                  <c:v>0.63831094307495673</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.350593297829709</c:v>
+                  <c:v>0.35059329782970872</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.838584978682301</c:v>
+                  <c:v>0.8385849786823002</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.831397228300744</c:v>
+                  <c:v>0.83139722830074225</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.99301676060078</c:v>
+                  <c:v>0.99301676060078015</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9983-4F0F-80F4-002E112B287C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>251202_pairwise_distances!$M$1</c:f>
+              <c:f>'251202_pairwise_distances'!$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1095,7 +1181,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ffd320"/>
+              <a:srgbClr val="FFD320"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -1103,16 +1189,24 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="sv-SE"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1120,40 +1214,41 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="0">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>251202_pairwise_distances!$M$2:$M$16</c:f>
+              <c:f>'251202_pairwise_distances'!$M$2:$M$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.981924262846429</c:v>
+                  <c:v>0.98192426284642886</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0752150642869971</c:v>
+                  <c:v>7.5215064286997479E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0513282970862132</c:v>
+                  <c:v>5.1328297086212879E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.459016092969441</c:v>
+                  <c:v>0.45901609296944051</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1</c:v>
@@ -1162,42 +1257,47 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.297739497343149</c:v>
+                  <c:v>0.29773949734314903</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.864579228673523</c:v>
+                  <c:v>0.86457922867352255</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.850011389018827</c:v>
+                  <c:v>0.85001138901882678</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.634895451397799</c:v>
+                  <c:v>0.63489545139779835</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.0889461763362</c:v>
+                  <c:v>8.8946176336199556E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.0654438704879399</c:v>
+                  <c:v>6.5443870487939121E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.436317820001977</c:v>
+                  <c:v>0.43631782000197633</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.366997957526424</c:v>
+                  <c:v>0.36699795752642367</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.80878726192359</c:v>
+                  <c:v>0.80878726192359129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9983-4F0F-80F4-002E112B287C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>251202_pairwise_distances!$O$1</c:f>
+              <c:f>'251202_pairwise_distances'!$O$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1208,7 +1308,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="579d1c"/>
+              <a:srgbClr val="579D1C"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -1216,16 +1316,24 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="sv-SE"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1233,26 +1341,27 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="0">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>251202_pairwise_distances!$O$2:$O$16</c:f>
+              <c:f>'251202_pairwise_distances'!$O$2:$O$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -1263,40 +1372,40 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5</c:v>
+                  <c:v>0.49999999999999989</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.75</c:v>
+                  <c:v>0.75000000000000011</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.75</c:v>
+                  <c:v>0.75000000000000011</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5</c:v>
+                  <c:v>0.49999999999999989</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.75</c:v>
+                  <c:v>0.75000000000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.75</c:v>
+                  <c:v>0.75000000000000011</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.25</c:v>
+                  <c:v>0.24999999999999994</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.75</c:v>
+                  <c:v>0.75000000000000011</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.5</c:v>
+                  <c:v>0.49999999999999989</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>1</c:v>
@@ -1304,9 +1413,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-9983-4F0F-80F4-002E112B287C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="100"/>
-        <c:overlap val="0"/>
         <c:axId val="72091839"/>
         <c:axId val="83759063"/>
       </c:barChart>
@@ -1324,7 +1445,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -1333,11 +1454,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="sv-SE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="83759063"/>
@@ -1358,7 +1480,7 @@
           <c:spPr>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
+                <a:srgbClr val="B3B3B3"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -1370,7 +1492,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -1379,11 +1501,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="sv-SE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="72091839"/>
@@ -1394,7 +1517,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="b3b3b3"/>
+            <a:srgbClr val="B3B3B3"/>
           </a:solidFill>
         </a:ln>
       </c:spPr>
@@ -1413,30 +1536,37 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
               <a:uFillTx/>
               <a:latin typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="sv-SE"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -1450,14 +1580,20 @@
       <xdr:row>53</xdr:row>
       <xdr:rowOff>123840</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="1053720" y="3039480"/>
-        <a:ext cx="10133640" cy="5699880"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1480,14 +1616,20 @@
       <xdr:row>53</xdr:row>
       <xdr:rowOff>100800</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="11315880" y="2915640"/>
-        <a:ext cx="10312920" cy="5800680"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1501,56 +1643,56 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -1603,71 +1745,70 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O57"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="30.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="23.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15"/>
+    <col min="1" max="1" width="5" style="1" customWidth="1"/>
+    <col min="2" max="5" width="30" customWidth="1"/>
+    <col min="6" max="8" width="23.21875" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1676,52 +1817,52 @@
       <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>1.04345805589899E-005</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>3.32251380339169E-005</v>
-      </c>
-      <c r="F2" s="4" t="n">
+      <c r="D2" s="3">
+        <v>1.04345805589899E-5</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3.3225138033916899E-5</v>
+      </c>
+      <c r="F2" s="4">
         <v>0.446540880503145</v>
       </c>
-      <c r="G2" s="0" t="n">
-        <f aca="false">1-D2*10000</f>
-        <v>0.895654194410101</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <f aca="false">1-E2*10000</f>
-        <v>0.667748619660831</v>
-      </c>
-      <c r="I2" s="0" t="n">
+      <c r="G2">
+        <f t="shared" ref="G2:G16" si="0">1-D2*10000</f>
+        <v>0.89565419441010097</v>
+      </c>
+      <c r="H2">
+        <f t="shared" ref="H2:H16" si="1">1-E2*10000</f>
+        <v>0.66774861966083099</v>
+      </c>
+      <c r="I2">
         <v>0.7</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2">
         <v>0.9</v>
       </c>
-      <c r="K2" s="0" t="n">
-        <f aca="false">(F2-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
+      <c r="K2">
+        <f t="shared" ref="K2:K16" si="2">(F2-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
         <v>1</v>
       </c>
-      <c r="L2" s="0" t="n">
-        <f aca="false">(G2-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.924367744880404</v>
-      </c>
-      <c r="M2" s="0" t="n">
-        <f aca="false">(H2-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.981924262846429</v>
-      </c>
-      <c r="N2" s="0" t="n">
-        <f aca="false">(I2-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
-        <v>0.5</v>
-      </c>
-      <c r="O2" s="0" t="n">
-        <f aca="false">(J2-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
+      <c r="L2">
+        <f t="shared" ref="L2:L16" si="3">(G2-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
+        <v>0.92436774488040274</v>
+      </c>
+      <c r="M2">
+        <f t="shared" ref="M2:M16" si="4">(H2-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
+        <v>0.98192426284642886</v>
+      </c>
+      <c r="N2">
+        <f t="shared" ref="N2:N16" si="5">(I2-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
+        <v>0.49999999999999989</v>
+      </c>
+      <c r="O2">
+        <f t="shared" ref="O2:O16" si="6">(J2-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1730,52 +1871,52 @@
       <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>2.548852930902E-005</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>9.15577012939986E-005</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0.345911949685535</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <f aca="false">1-D3*10000</f>
-        <v>0.7451147069098</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <f aca="false">1-E3*10000</f>
-        <v>0.0844229870600136</v>
-      </c>
-      <c r="I3" s="0" t="n">
+      <c r="D3" s="3">
+        <v>2.5488529309019999E-5</v>
+      </c>
+      <c r="E3" s="3">
+        <v>9.1557701293998599E-5</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.34591194968553501</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="0"/>
+        <v>0.74511470690980008</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="1"/>
+        <v>8.4422987060014054E-2</v>
+      </c>
+      <c r="I3">
         <v>0.7</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3">
         <v>0.5</v>
       </c>
-      <c r="K3" s="0" t="n">
-        <f aca="false">(F3-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.705421070576202</v>
-      </c>
-      <c r="L3" s="0" t="n">
-        <f aca="false">(G3-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.207655027063344</v>
-      </c>
-      <c r="M3" s="0" t="n">
-        <f aca="false">(H3-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.0752150642869971</v>
-      </c>
-      <c r="N3" s="0" t="n">
-        <f aca="false">(I3-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
-        <v>0.5</v>
-      </c>
-      <c r="O3" s="0" t="n">
-        <f aca="false">(J3-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
+      <c r="K3">
+        <f t="shared" si="2"/>
+        <v>0.70542107057620262</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="3"/>
+        <v>0.20765502706334077</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="4"/>
+        <v>7.5215064286997479E-2</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="5"/>
+        <v>0.49999999999999989</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1784,52 +1925,52 @@
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>1.56077365644848E-005</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>9.30944413657133E-005</v>
-      </c>
-      <c r="F4" s="4" t="n">
+      <c r="D4" s="3">
+        <v>1.5607736564484801E-5</v>
+      </c>
+      <c r="E4" s="3">
+        <v>9.3094441365713305E-5</v>
+      </c>
+      <c r="F4" s="4">
         <v>0.104938271604938</v>
       </c>
-      <c r="G4" s="0" t="n">
-        <f aca="false">1-D4*10000</f>
-        <v>0.843922634355152</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <f aca="false">1-E4*10000</f>
-        <v>0.0690555863428669</v>
-      </c>
-      <c r="I4" s="0" t="n">
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>0.84392263435515202</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>6.9055586342866904E-2</v>
+      </c>
+      <c r="I4">
         <v>0.5</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4">
         <v>0.7</v>
       </c>
-      <c r="K4" s="0" t="n">
-        <f aca="false">(F4-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
+      <c r="K4">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L4" s="0" t="n">
-        <f aca="false">(G4-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.678075774450885</v>
-      </c>
-      <c r="M4" s="0" t="n">
-        <f aca="false">(H4-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.0513282970862132</v>
-      </c>
-      <c r="N4" s="0" t="n">
-        <f aca="false">(I4-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
+      <c r="L4">
+        <f t="shared" si="3"/>
+        <v>0.67807577445088396</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="4"/>
+        <v>5.1328297086212879E-2</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O4" s="0" t="n">
-        <f aca="false">(J4-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
-        <v>0.5</v>
+      <c r="O4">
+        <f t="shared" si="6"/>
+        <v>0.49999999999999989</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1838,52 +1979,52 @@
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>1.34174007666941E-005</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>6.68661046713185E-005</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0.415094339622642</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <f aca="false">1-D5*10000</f>
-        <v>0.865825992333059</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <f aca="false">1-E5*10000</f>
-        <v>0.331338953286816</v>
-      </c>
-      <c r="I5" s="0" t="n">
+      <c r="D5" s="3">
+        <v>1.34174007666941E-5</v>
+      </c>
+      <c r="E5" s="3">
+        <v>6.6866104671318494E-5</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.41509433962264197</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>0.86582599233305901</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>0.33133895328681506</v>
+      </c>
+      <c r="I5">
         <v>0.8</v>
       </c>
-      <c r="J5" s="0" t="n">
+      <c r="J5">
         <v>0.8</v>
       </c>
-      <c r="K5" s="0" t="n">
-        <f aca="false">(F5-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.907944084555063</v>
-      </c>
-      <c r="L5" s="0" t="n">
-        <f aca="false">(G5-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.782356820482973</v>
-      </c>
-      <c r="M5" s="0" t="n">
-        <f aca="false">(H5-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.459016092969441</v>
-      </c>
-      <c r="N5" s="0" t="n">
-        <f aca="false">(I5-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
-        <v>0.75</v>
-      </c>
-      <c r="O5" s="0" t="n">
-        <f aca="false">(J5-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
-        <v>0.75</v>
+      <c r="K5">
+        <f t="shared" si="2"/>
+        <v>0.90794408455506359</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="3"/>
+        <v>0.7823568204829715</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="4"/>
+        <v>0.45901609296944051</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="5"/>
+        <v>0.75000000000000011</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="6"/>
+        <v>0.75000000000000011</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1892,52 +2033,52 @@
       <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>1.41584309262414E-005</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>3.2062246907789E-005</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="D6" s="3">
+        <v>1.4158430926241401E-5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.2062246907789E-5</v>
+      </c>
+      <c r="F6" s="4">
         <v>0.320754716981132</v>
       </c>
-      <c r="G6" s="0" t="n">
-        <f aca="false">1-D6*10000</f>
-        <v>0.858415690737586</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <f aca="false">1-E6*10000</f>
-        <v>0.67937753092211</v>
-      </c>
-      <c r="I6" s="0" t="n">
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>0.85841569073758595</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>0.67937753092210995</v>
+      </c>
+      <c r="I6">
         <v>0.7</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6">
         <v>0.8</v>
       </c>
-      <c r="K6" s="0" t="n">
-        <f aca="false">(F6-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.631776338220252</v>
-      </c>
-      <c r="L6" s="0" t="n">
-        <f aca="false">(G6-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.747076659214157</v>
-      </c>
-      <c r="M6" s="0" t="n">
-        <f aca="false">(H6-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>0.6317763382202517</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="3"/>
+        <v>0.74707665921415489</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="N6" s="0" t="n">
-        <f aca="false">(I6-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
-        <v>0.5</v>
-      </c>
-      <c r="O6" s="0" t="n">
-        <f aca="false">(J6-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
-        <v>0.75</v>
+      <c r="N6">
+        <f t="shared" si="5"/>
+        <v>0.49999999999999989</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="6"/>
+        <v>0.75000000000000011</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1946,52 +2087,52 @@
       <c r="C7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>1.94035347739049E-005</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>9.63966149198923E-005</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0.239130434782609</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <f aca="false">1-D7*10000</f>
-        <v>0.805964652260952</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <f aca="false">1-E7*10000</f>
-        <v>0.0360338508010768</v>
-      </c>
-      <c r="I7" s="0" t="n">
+      <c r="D7" s="3">
+        <v>1.9403534773904901E-5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>9.6396614919892298E-5</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.23913043478260901</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>0.80596465226095093</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>3.6033850801077016E-2</v>
+      </c>
+      <c r="I7">
         <v>0.8</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7">
         <v>0.5</v>
       </c>
-      <c r="K7" s="0" t="n">
-        <f aca="false">(F7-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.392831201174047</v>
-      </c>
-      <c r="L7" s="0" t="n">
-        <f aca="false">(G7-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.49735927965392</v>
-      </c>
-      <c r="M7" s="0" t="n">
-        <f aca="false">(H7-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>0.39283120117404752</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="3"/>
+        <v>0.49735927965391669</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N7" s="0" t="n">
-        <f aca="false">(I7-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
-        <v>0.75</v>
-      </c>
-      <c r="O7" s="0" t="n">
-        <f aca="false">(J7-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
+      <c r="N7">
+        <f t="shared" si="5"/>
+        <v>0.75000000000000011</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2000,52 +2141,52 @@
       <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="3" t="n">
-        <v>1.13270651531941E-005</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>7.72417325260795E-005</v>
-      </c>
-      <c r="F8" s="4" t="n">
+      <c r="D8" s="3">
+        <v>1.1327065153194101E-5</v>
+      </c>
+      <c r="E8" s="3">
+        <v>7.7241732526079496E-5</v>
+      </c>
+      <c r="F8" s="4">
         <v>0.25</v>
       </c>
-      <c r="G8" s="0" t="n">
-        <f aca="false">1-D8*10000</f>
-        <v>0.886729348468059</v>
-      </c>
-      <c r="H8" s="0" t="n">
-        <f aca="false">1-E8*10000</f>
-        <v>0.227582674739205</v>
-      </c>
-      <c r="I8" s="0" t="n">
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>0.88672934846805895</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>0.22758267473920502</v>
+      </c>
+      <c r="I8">
         <v>0.6</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8">
         <v>0.7</v>
       </c>
-      <c r="K8" s="0" t="n">
-        <f aca="false">(F8-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.424650528469144</v>
-      </c>
-      <c r="L8" s="0" t="n">
-        <f aca="false">(G8-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.881876896150718</v>
-      </c>
-      <c r="M8" s="0" t="n">
-        <f aca="false">(H8-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.297739497343149</v>
-      </c>
-      <c r="N8" s="0" t="n">
-        <f aca="false">(I8-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
-        <v>0.25</v>
-      </c>
-      <c r="O8" s="0" t="n">
-        <f aca="false">(J8-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
-        <v>0.5</v>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>0.4246505284691442</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="3"/>
+        <v>0.88187689615071829</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="4"/>
+        <v>0.29773949734314903</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="5"/>
+        <v>0.24999999999999994</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="6"/>
+        <v>0.49999999999999989</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -2054,52 +2195,52 @@
       <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>8.84598855536617E-006</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>4.07744566467895E-005</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0.27536231884058</v>
-      </c>
-      <c r="G9" s="0" t="n">
-        <f aca="false">1-D9*10000</f>
-        <v>0.911540114446338</v>
-      </c>
-      <c r="H9" s="0" t="n">
-        <f aca="false">1-E9*10000</f>
-        <v>0.592255433532106</v>
-      </c>
-      <c r="I9" s="0" t="n">
+      <c r="D9" s="3">
+        <v>8.8459885553661696E-6</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4.07744566467895E-5</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.27536231884057999</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>0.91154011444633831</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>0.59225543353210508</v>
+      </c>
+      <c r="I9">
         <v>0.8</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J9">
         <v>0.9</v>
       </c>
-      <c r="K9" s="0" t="n">
-        <f aca="false">(F9-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.498895625491039</v>
-      </c>
-      <c r="L9" s="0" t="n">
-        <f aca="false">(G9-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>0.49889562549103966</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M9" s="0" t="n">
-        <f aca="false">(H9-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.864579228673523</v>
-      </c>
-      <c r="N9" s="0" t="n">
-        <f aca="false">(I9-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
-        <v>0.75</v>
-      </c>
-      <c r="O9" s="0" t="n">
-        <f aca="false">(J9-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
+      <c r="M9">
+        <f t="shared" si="4"/>
+        <v>0.86457922867352255</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="5"/>
+        <v>0.75000000000000011</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -2108,52 +2249,52 @@
       <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>1.03649736819894E-005</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>4.1711669404276E-005</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.384057971014493</v>
-      </c>
-      <c r="G10" s="0" t="n">
-        <f aca="false">1-D10*10000</f>
-        <v>0.896350263180106</v>
-      </c>
-      <c r="H10" s="0" t="n">
-        <f aca="false">1-E10*10000</f>
-        <v>0.58288330595724</v>
-      </c>
-      <c r="I10" s="0" t="n">
+      <c r="D10" s="3">
+        <v>1.03649736819894E-5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4.1711669404276003E-5</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.38405797101449302</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>0.89635026318010602</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>0.58288330595724003</v>
+      </c>
+      <c r="I10">
         <v>0.7</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J10">
         <v>0.8</v>
       </c>
-      <c r="K10" s="0" t="n">
-        <f aca="false">(F10-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.817088898442017</v>
-      </c>
-      <c r="L10" s="0" t="n">
-        <f aca="false">(G10-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.927681701558628</v>
-      </c>
-      <c r="M10" s="0" t="n">
-        <f aca="false">(H10-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.850011389018827</v>
-      </c>
-      <c r="N10" s="0" t="n">
-        <f aca="false">(I10-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
-        <v>0.5</v>
-      </c>
-      <c r="O10" s="0" t="n">
-        <f aca="false">(J10-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
-        <v>0.75</v>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>0.81708889844201671</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="3"/>
+        <v>0.92768170155862573</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="4"/>
+        <v>0.85001138901882678</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="5"/>
+        <v>0.49999999999999989</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="6"/>
+        <v>0.75000000000000011</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -2162,52 +2303,52 @@
       <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>1.64429634534537E-005</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>5.55510173004559E-005</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0.191358024691358</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <f aca="false">1-D11*10000</f>
-        <v>0.835570365465463</v>
-      </c>
-      <c r="H11" s="0" t="n">
-        <f aca="false">1-E11*10000</f>
-        <v>0.444489826995442</v>
-      </c>
-      <c r="I11" s="0" t="n">
+      <c r="D11" s="3">
+        <v>1.6442963453453702E-5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>5.5551017300455899E-5</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0.19135802469135799</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>0.83557036546546293</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>0.44448982699544104</v>
+      </c>
+      <c r="I11">
         <v>0.5</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="J11">
         <v>0.8</v>
       </c>
-      <c r="K11" s="0" t="n">
-        <f aca="false">(F11-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.252983293556086</v>
-      </c>
-      <c r="L11" s="0" t="n">
-        <f aca="false">(G11-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.638310943074958</v>
-      </c>
-      <c r="M11" s="0" t="n">
-        <f aca="false">(H11-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.634895451397799</v>
-      </c>
-      <c r="N11" s="0" t="n">
-        <f aca="false">(I11-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>0.25298329355608618</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>0.63831094307495673</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="4"/>
+        <v>0.63489545139779835</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="0" t="n">
-        <f aca="false">(J11-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
-        <v>0.75</v>
+      <c r="O11">
+        <f t="shared" si="6"/>
+        <v>0.75000000000000011</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -2216,52 +2357,52 @@
       <c r="C12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>2.24862309696119E-005</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>9.06743188782098E-005</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0.151515151515152</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <f aca="false">1-D12*10000</f>
-        <v>0.775137690303881</v>
-      </c>
-      <c r="H12" s="0" t="n">
-        <f aca="false">1-E12*10000</f>
-        <v>0.0932568112179021</v>
-      </c>
-      <c r="I12" s="0" t="n">
+      <c r="D12" s="3">
+        <v>2.24862309696119E-5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>9.06743188782098E-5</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0.15151515151515199</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>0.77513769030388102</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>9.3256811217901969E-2</v>
+      </c>
+      <c r="I12">
         <v>0.7</v>
       </c>
-      <c r="J12" s="0" t="n">
+      <c r="J12">
         <v>0.6</v>
       </c>
-      <c r="K12" s="0" t="n">
-        <f aca="false">(F12-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.136348138734774</v>
-      </c>
-      <c r="L12" s="0" t="n">
-        <f aca="false">(G12-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.350593297829709</v>
-      </c>
-      <c r="M12" s="0" t="n">
-        <f aca="false">(H12-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.0889461763362</v>
-      </c>
-      <c r="N12" s="0" t="n">
-        <f aca="false">(I12-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
-        <v>0.5</v>
-      </c>
-      <c r="O12" s="0" t="n">
-        <f aca="false">(J12-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
-        <v>0.25</v>
+      <c r="K12">
+        <f t="shared" si="2"/>
+        <v>0.13634813873477553</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="3"/>
+        <v>0.35059329782970872</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="4"/>
+        <v>8.8946176336199556E-2</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="5"/>
+        <v>0.49999999999999989</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="6"/>
+        <v>0.24999999999999994</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -2270,52 +2411,52 @@
       <c r="C13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="3" t="n">
-        <v>2.98501487660024E-005</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>9.21863248717848E-005</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0.196261682242991</v>
-      </c>
-      <c r="G13" s="0" t="n">
-        <f aca="false">1-D13*10000</f>
-        <v>0.701498512339976</v>
-      </c>
-      <c r="H13" s="0" t="n">
-        <f aca="false">1-E13*10000</f>
-        <v>0.0781367512821524</v>
-      </c>
-      <c r="I13" s="0" t="n">
+      <c r="D13" s="3">
+        <v>2.98501487660024E-5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>9.2186324871784803E-5</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0.19626168224299101</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>0.70149851233997595</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>7.8136751282152028E-2</v>
+      </c>
+      <c r="I13">
         <v>0.6</v>
       </c>
-      <c r="J13" s="0" t="n">
+      <c r="J13">
         <v>0.5</v>
       </c>
-      <c r="K13" s="0" t="n">
-        <f aca="false">(F13-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.267338153337306</v>
-      </c>
-      <c r="L13" s="0" t="n">
-        <f aca="false">(G13-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
+      <c r="K13">
+        <f t="shared" si="2"/>
+        <v>0.26733815333730709</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M13" s="0" t="n">
-        <f aca="false">(H13-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.0654438704879399</v>
-      </c>
-      <c r="N13" s="0" t="n">
-        <f aca="false">(I13-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
-        <v>0.25</v>
-      </c>
-      <c r="O13" s="0" t="n">
-        <f aca="false">(J13-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
+      <c r="M13">
+        <f t="shared" si="4"/>
+        <v>6.5443870487939121E-2</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="5"/>
+        <v>0.24999999999999994</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -2324,52 +2465,52 @@
       <c r="C14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>1.22363755235264E-005</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>6.83263837176465E-005</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0.200617283950617</v>
-      </c>
-      <c r="G14" s="0" t="n">
-        <f aca="false">1-D14*10000</f>
-        <v>0.877636244764736</v>
-      </c>
-      <c r="H14" s="0" t="n">
-        <f aca="false">1-E14*10000</f>
-        <v>0.316736162823535</v>
-      </c>
-      <c r="I14" s="0" t="n">
+      <c r="D14" s="3">
+        <v>1.2236375523526399E-5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6.8326383717646507E-5</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.20061728395061701</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>0.87763624476473601</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>0.31673616282353489</v>
+      </c>
+      <c r="I14">
         <v>0.6</v>
       </c>
-      <c r="J14" s="0" t="n">
+      <c r="J14">
         <v>0.8</v>
       </c>
-      <c r="K14" s="0" t="n">
-        <f aca="false">(F14-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.280088646437095</v>
-      </c>
-      <c r="L14" s="0" t="n">
-        <f aca="false">(G14-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.838584978682301</v>
-      </c>
-      <c r="M14" s="0" t="n">
-        <f aca="false">(H14-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.436317820001977</v>
-      </c>
-      <c r="N14" s="0" t="n">
-        <f aca="false">(I14-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
-        <v>0.25</v>
-      </c>
-      <c r="O14" s="0" t="n">
-        <f aca="false">(J14-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
-        <v>0.75</v>
+      <c r="K14">
+        <f t="shared" si="2"/>
+        <v>0.28008864643709463</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="3"/>
+        <v>0.8385849786823002</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="4"/>
+        <v>0.43631782000197633</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="5"/>
+        <v>0.24999999999999994</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="6"/>
+        <v>0.75000000000000011</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -2378,52 +2519,52 @@
       <c r="C15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>1.23873481840947E-005</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>7.27860332606971E-005</v>
-      </c>
-      <c r="F15" s="4" t="n">
+      <c r="D15" s="3">
+        <v>1.23873481840947E-5</v>
+      </c>
+      <c r="E15" s="3">
+        <v>7.2786033260697098E-5</v>
+      </c>
+      <c r="F15" s="4">
         <v>0.157407407407407</v>
       </c>
-      <c r="G15" s="0" t="n">
-        <f aca="false">1-D15*10000</f>
-        <v>0.876126518159053</v>
-      </c>
-      <c r="H15" s="0" t="n">
-        <f aca="false">1-E15*10000</f>
-        <v>0.272139667393029</v>
-      </c>
-      <c r="I15" s="0" t="n">
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>0.87612651815905296</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>0.27213966739302897</v>
+      </c>
+      <c r="I15">
         <v>0.7</v>
       </c>
-      <c r="J15" s="0" t="n">
+      <c r="J15">
         <v>0.7</v>
       </c>
-      <c r="K15" s="0" t="n">
-        <f aca="false">(F15-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.153596999659052</v>
-      </c>
-      <c r="L15" s="0" t="n">
-        <f aca="false">(G15-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.831397228300744</v>
-      </c>
-      <c r="M15" s="0" t="n">
-        <f aca="false">(H15-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.366997957526424</v>
-      </c>
-      <c r="N15" s="0" t="n">
-        <f aca="false">(I15-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
-        <v>0.5</v>
-      </c>
-      <c r="O15" s="0" t="n">
-        <f aca="false">(J15-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
-        <v>0.5</v>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>0.15359699965905149</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="3"/>
+        <v>0.83139722830074225</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="4"/>
+        <v>0.36699795752642367</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="5"/>
+        <v>0.49999999999999989</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="6"/>
+        <v>0.49999999999999989</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -2432,55 +2573,59 @@
       <c r="C16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>8.99266563449661E-006</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>4.43637975677986E-005</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0.196261682242991</v>
-      </c>
-      <c r="G16" s="0" t="n">
-        <f aca="false">1-D16*10000</f>
-        <v>0.910073343655034</v>
-      </c>
-      <c r="H16" s="0" t="n">
-        <f aca="false">1-E16*10000</f>
-        <v>0.556362024322014</v>
-      </c>
-      <c r="I16" s="0" t="n">
+      <c r="D16" s="3">
+        <v>8.9926656344966094E-6</v>
+      </c>
+      <c r="E16" s="3">
+        <v>4.4363797567798598E-5</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.19626168224299101</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>0.9100733436550339</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>0.55636202432201398</v>
+      </c>
+      <c r="I16">
         <v>0.9</v>
       </c>
-      <c r="J16" s="0" t="n">
+      <c r="J16">
         <v>0.9</v>
       </c>
-      <c r="K16" s="0" t="n">
-        <f aca="false">(F16-MIN(F$2:F$16))/(MAX(F$2:F$16)-MIN(F$2:F$16))</f>
-        <v>0.267338153337306</v>
-      </c>
-      <c r="L16" s="0" t="n">
-        <f aca="false">(G16-MIN(G$2:G$16))/(MAX(G$2:G$16)-MIN(G$2:G$16))</f>
-        <v>0.99301676060078</v>
-      </c>
-      <c r="M16" s="0" t="n">
-        <f aca="false">(H16-MIN(H$2:H$16))/(MAX(H$2:H$16)-MIN(H$2:H$16))</f>
-        <v>0.80878726192359</v>
-      </c>
-      <c r="N16" s="0" t="n">
-        <f aca="false">(I16-MIN(I$2:I$16))/(MAX(I$2:I$16)-MIN(I$2:I$16))</f>
+      <c r="K16">
+        <f t="shared" si="2"/>
+        <v>0.26733815333730709</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="3"/>
+        <v>0.99301676060078015</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="4"/>
+        <v>0.80878726192359129</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="O16" s="0" t="n">
-        <f aca="false">(J16-MIN(J$2:J$16))/(MAX(J$2:J$16)-MIN(J$2:J$16))</f>
+      <c r="O16">
+        <f t="shared" si="6"/>
         <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="4:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
